--- a/InputData/elec/DRC/Demand Response Capacity.xlsx
+++ b/InputData/elec/DRC/Demand Response Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\DRC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\elec\DRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845A6FAA-504D-4C75-BC8B-E953DE6936DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726D1944-1CAD-447D-897B-E50B30316ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -533,32 +533,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="107.28515625" customWidth="1"/>
+    <col min="2" max="2" width="107.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -566,92 +566,92 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" s="2">
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -669,19 +669,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -689,7 +689,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>59000</v>
       </c>
@@ -697,44 +697,44 @@
         <v>198000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20">
         <v>4</v>
       </c>
@@ -751,12 +751,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -860,7 +860,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1008,12 +1008,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1265,13 +1265,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.1328125" customWidth="1"/>
+    <col min="2" max="2" width="17.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
@@ -1279,12 +1279,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="4">
-        <f>'Data and Calculations'!A20</f>
+        <f>ROUND('Data and Calculations'!A20,0)</f>
         <v>4</v>
       </c>
       <c r="C2" s="4"/>
